--- a/backend/tests/fixtures/Bureaux_Centraux.xlsx
+++ b/backend/tests/fixtures/Bureaux_Centraux.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,46 @@
           <t>نائب العضو الثالث</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>رقم البطاقة الوطنية - الرئيس</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>رقم البطاقة الوطنية - نائب الرئيس</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>رقم البطاقة الوطنية - العضو الأول</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>رقم البطاقة الوطنية - العضو الثاني</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>رقم البطاقة الوطنية - كاتب</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>رقم البطاقة الوطنية - نائب العضو الأول</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>رقم البطاقة الوطنية - نائب العضو الثاني</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>رقم البطاقة الوطنية - نائب الكاتب</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -527,6 +567,46 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>نائب ج</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>P8</t>
         </is>
       </c>
     </row>

--- a/backend/tests/fixtures/Bureaux_Centraux.xlsx
+++ b/backend/tests/fixtures/Bureaux_Centraux.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bureaux_Centraux" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مكاتب التصويت المركزية" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,189 +419,189 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>رئيس المكتب المركزي</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>بطاقة التعريف الوطنية رئيس المكتب المركزي</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>رقم المكتب المركزي</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>الجماعة</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>رقم المكتب المركزي</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>رئيس المكتب المركزي</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>عنوان المكتب المركزي</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>عنوان مكتب التصويت</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>نائب رئيس المكتب المركزي</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>بطاقة التعريف الوطنية نائب رئيس المكتب المركزي</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>العضو الأول</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>بطاقة التعريف الوطنية عضو الأول</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>العضو الثاني</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>بطاقة التعريف الوطنية عضو الثاني</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>العضو الثالث</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>بطاقة التعريف الوطنية عضو الثالث</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>نائب العضو الأول</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>بطاقة التعريف الوطنية نائب العضو الأول</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>نائب العضو الثاني</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>بطاقة التعريف الوطنية نائب العضو الثاني</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>نائب العضو الثالث</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>رقم البطاقة الوطنية - الرئيس</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>رقم البطاقة الوطنية - نائب الرئيس</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>رقم البطاقة الوطنية - العضو الأول</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>رقم البطاقة الوطنية - العضو الثاني</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>رقم البطاقة الوطنية - كاتب</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>رقم البطاقة الوطنية - نائب العضو الأول</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>رقم البطاقة الوطنية - نائب العضو الثاني</t>
-        </is>
-      </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>رقم البطاقة الوطنية - نائب الكاتب</t>
+          <t>بطاقة التعريف الوطنية نائب العضو الثالث</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>عبد الحق بلعابد</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>الداخلة</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>عبد الحق بلعابد</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>المدرسة المركزية</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>نائب الرئيس</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>عضو أ</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>عضو ب</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>عضو ج</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>نائب أ</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>نائب ب</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>نائب ج</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>P6</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>P7</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -613,55 +613,55 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>محمد أمين الشرقي</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>الداخلة</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>محمد أمين الشرقي</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>مقر آخر</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>نائب آخر</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>عضو د</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>عضو ه</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>عضو و</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>نائب د</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>نائب ه</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>نائب و</t>
         </is>
@@ -670,46 +670,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>الحبيب العسري</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>اگويرة</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>الحبيب العسري</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>عبد الحق بلعابد (dup)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>الداخلة</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>عبد الحق بلعابد (dup)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>رئيس بدون رقم</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>الداخلة</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>رئيس بدون رقم</t>
         </is>
       </c>
     </row>
